--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_23.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_23.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="34">
   <si>
     <t>Result</t>
   </si>
@@ -130,12 +130,16 @@
   </si>
   <si>
     <t>Pay Now Credit Card, Emulator Data is overwritten</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:11:55 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -515,11 +519,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
+      <c r="B2" t="s" s="0">
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -609,10 +613,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>30</v>
       </c>
       <c r="C2" s="3"/>
@@ -703,10 +707,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="C2" s="3"/>
@@ -1017,78 +1021,78 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>35</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>6425</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>2</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <v>5</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="0">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>3</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <v>3</v>
       </c>
     </row>

--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_23.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_23.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
   <si>
     <t>Result</t>
   </si>
@@ -133,6 +133,42 @@
   </si>
   <si>
     <t>Mon Aug 31 21:11:55 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 06:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 06:54:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 06:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 06:58:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:02:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:04:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:05:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:07:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 07:08:07 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -523,7 +559,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -617,7 +653,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -711,7 +747,7 @@
         <v>27</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1065,6 +1101,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>39</v>
+      </c>
       <c r="C2" t="s" s="0">
         <v>32</v>
       </c>
